--- a/data/out/goals_merged.xlsx
+++ b/data/out/goals_merged.xlsx
@@ -7651,6 +7651,12 @@
       <c r="AW37">
         <v>1892</v>
       </c>
+      <c r="AX37">
+        <v>1874</v>
+      </c>
+      <c r="AY37">
+        <v>1832</v>
+      </c>
     </row>
     <row r="38" spans="1:51">
       <c r="A38">
@@ -7800,6 +7806,12 @@
       <c r="AW38">
         <v>1892</v>
       </c>
+      <c r="AX38">
+        <v>1874</v>
+      </c>
+      <c r="AY38">
+        <v>1832</v>
+      </c>
     </row>
     <row r="39" spans="1:51">
       <c r="A39">
@@ -7949,6 +7961,12 @@
       <c r="AW39">
         <v>1892</v>
       </c>
+      <c r="AX39">
+        <v>1874</v>
+      </c>
+      <c r="AY39">
+        <v>1832</v>
+      </c>
     </row>
     <row r="40" spans="1:51">
       <c r="A40">
@@ -15475,7 +15493,13 @@
         <v>1987</v>
       </c>
       <c r="AW89">
+        <v>1863</v>
+      </c>
+      <c r="AX89">
         <v>1854</v>
+      </c>
+      <c r="AY89">
+        <v>1852</v>
       </c>
     </row>
     <row r="90" spans="1:51">
@@ -15624,7 +15648,13 @@
         <v>1987</v>
       </c>
       <c r="AW90">
+        <v>1863</v>
+      </c>
+      <c r="AX90">
         <v>1854</v>
+      </c>
+      <c r="AY90">
+        <v>1852</v>
       </c>
     </row>
     <row r="91" spans="1:51">
@@ -15773,7 +15803,13 @@
         <v>1987</v>
       </c>
       <c r="AW91">
+        <v>1863</v>
+      </c>
+      <c r="AX91">
         <v>1854</v>
+      </c>
+      <c r="AY91">
+        <v>1852</v>
       </c>
     </row>
     <row r="92" spans="1:51">
@@ -29381,7 +29417,13 @@
         <v>2017</v>
       </c>
       <c r="AW181">
+        <v>1925</v>
+      </c>
+      <c r="AX181">
         <v>1868</v>
+      </c>
+      <c r="AY181">
+        <v>1769</v>
       </c>
     </row>
     <row r="182" spans="1:51">
@@ -29530,7 +29572,13 @@
         <v>2017</v>
       </c>
       <c r="AW182">
+        <v>1925</v>
+      </c>
+      <c r="AX182">
         <v>1868</v>
+      </c>
+      <c r="AY182">
+        <v>1769</v>
       </c>
     </row>
     <row r="183" spans="1:51">
@@ -29679,7 +29727,13 @@
         <v>2017</v>
       </c>
       <c r="AW183">
+        <v>1925</v>
+      </c>
+      <c r="AX183">
         <v>1868</v>
+      </c>
+      <c r="AY183">
+        <v>1769</v>
       </c>
     </row>
     <row r="184" spans="1:51">
@@ -38754,9 +38808,15 @@
         <v>1</v>
       </c>
       <c r="AV243">
+        <v>1996</v>
+      </c>
+      <c r="AW243">
+        <v>1923</v>
+      </c>
+      <c r="AX243">
         <v>1799</v>
       </c>
-      <c r="AW243">
+      <c r="AY243">
         <v>1763</v>
       </c>
     </row>
@@ -38903,9 +38963,15 @@
         <v>1763</v>
       </c>
       <c r="AV244">
+        <v>1996</v>
+      </c>
+      <c r="AW244">
+        <v>1923</v>
+      </c>
+      <c r="AX244">
         <v>1799</v>
       </c>
-      <c r="AW244">
+      <c r="AY244">
         <v>1763</v>
       </c>
     </row>
@@ -39052,9 +39118,15 @@
         <v>1763</v>
       </c>
       <c r="AV245">
+        <v>1996</v>
+      </c>
+      <c r="AW245">
+        <v>1923</v>
+      </c>
+      <c r="AX245">
         <v>1799</v>
       </c>
-      <c r="AW245">
+      <c r="AY245">
         <v>1763</v>
       </c>
     </row>
@@ -39201,9 +39273,15 @@
         <v>1763</v>
       </c>
       <c r="AV246">
+        <v>1996</v>
+      </c>
+      <c r="AW246">
+        <v>1923</v>
+      </c>
+      <c r="AX246">
         <v>1799</v>
       </c>
-      <c r="AW246">
+      <c r="AY246">
         <v>1763</v>
       </c>
     </row>
@@ -39350,9 +39428,15 @@
         <v>1763</v>
       </c>
       <c r="AV247">
+        <v>1996</v>
+      </c>
+      <c r="AW247">
+        <v>1923</v>
+      </c>
+      <c r="AX247">
         <v>1799</v>
       </c>
-      <c r="AW247">
+      <c r="AY247">
         <v>1763</v>
       </c>
     </row>
@@ -39499,9 +39583,15 @@
         <v>1763</v>
       </c>
       <c r="AV248">
+        <v>1996</v>
+      </c>
+      <c r="AW248">
+        <v>1923</v>
+      </c>
+      <c r="AX248">
         <v>1799</v>
       </c>
-      <c r="AW248">
+      <c r="AY248">
         <v>1763</v>
       </c>
     </row>
@@ -46255,7 +46345,13 @@
         <v>1937</v>
       </c>
       <c r="AW293">
+        <v>1765</v>
+      </c>
+      <c r="AX293">
         <v>1670</v>
+      </c>
+      <c r="AY293">
+        <v>1529</v>
       </c>
     </row>
     <row r="294" spans="1:51">
@@ -46404,7 +46500,13 @@
         <v>1937</v>
       </c>
       <c r="AW294">
+        <v>1765</v>
+      </c>
+      <c r="AX294">
         <v>1670</v>
+      </c>
+      <c r="AY294">
+        <v>1529</v>
       </c>
     </row>
     <row r="295" spans="1:51">
@@ -46553,7 +46655,13 @@
         <v>1937</v>
       </c>
       <c r="AW295">
+        <v>1765</v>
+      </c>
+      <c r="AX295">
         <v>1670</v>
+      </c>
+      <c r="AY295">
+        <v>1529</v>
       </c>
     </row>
     <row r="296" spans="1:51">
@@ -46702,7 +46810,13 @@
         <v>1937</v>
       </c>
       <c r="AW296">
+        <v>1765</v>
+      </c>
+      <c r="AX296">
         <v>1670</v>
+      </c>
+      <c r="AY296">
+        <v>1529</v>
       </c>
     </row>
     <row r="297" spans="1:51">
@@ -46851,7 +46965,13 @@
         <v>1937</v>
       </c>
       <c r="AW297">
+        <v>1765</v>
+      </c>
+      <c r="AX297">
         <v>1670</v>
+      </c>
+      <c r="AY297">
+        <v>1529</v>
       </c>
     </row>
     <row r="298" spans="1:51">
@@ -47000,7 +47120,13 @@
         <v>1937</v>
       </c>
       <c r="AW298">
+        <v>1765</v>
+      </c>
+      <c r="AX298">
         <v>1670</v>
+      </c>
+      <c r="AY298">
+        <v>1529</v>
       </c>
     </row>
     <row r="299" spans="1:51">
@@ -48338,9 +48464,15 @@
         <v>1</v>
       </c>
       <c r="AV307">
+        <v>2109</v>
+      </c>
+      <c r="AW307">
+        <v>1876</v>
+      </c>
+      <c r="AX307">
         <v>1741</v>
       </c>
-      <c r="AW307">
+      <c r="AY307">
         <v>1538</v>
       </c>
     </row>
@@ -48487,9 +48619,15 @@
         <v>1538</v>
       </c>
       <c r="AV308">
+        <v>2109</v>
+      </c>
+      <c r="AW308">
+        <v>1876</v>
+      </c>
+      <c r="AX308">
         <v>1741</v>
       </c>
-      <c r="AW308">
+      <c r="AY308">
         <v>1538</v>
       </c>
     </row>
@@ -48636,9 +48774,15 @@
         <v>1538</v>
       </c>
       <c r="AV309">
+        <v>2109</v>
+      </c>
+      <c r="AW309">
+        <v>1876</v>
+      </c>
+      <c r="AX309">
         <v>1741</v>
       </c>
-      <c r="AW309">
+      <c r="AY309">
         <v>1538</v>
       </c>
     </row>
@@ -48785,9 +48929,15 @@
         <v>1538</v>
       </c>
       <c r="AV310">
+        <v>2109</v>
+      </c>
+      <c r="AW310">
+        <v>1876</v>
+      </c>
+      <c r="AX310">
         <v>1741</v>
       </c>
-      <c r="AW310">
+      <c r="AY310">
         <v>1538</v>
       </c>
     </row>
@@ -48915,6 +49065,12 @@
       <c r="AW311">
         <v>1886</v>
       </c>
+      <c r="AX311">
+        <v>1762</v>
+      </c>
+      <c r="AY311">
+        <v>1715</v>
+      </c>
     </row>
     <row r="312" spans="1:51">
       <c r="A312">
@@ -49064,6 +49220,12 @@
       <c r="AW312">
         <v>1886</v>
       </c>
+      <c r="AX312">
+        <v>1762</v>
+      </c>
+      <c r="AY312">
+        <v>1715</v>
+      </c>
     </row>
     <row r="313" spans="1:51">
       <c r="A313">
@@ -49213,6 +49375,12 @@
       <c r="AW313">
         <v>1886</v>
       </c>
+      <c r="AX313">
+        <v>1762</v>
+      </c>
+      <c r="AY313">
+        <v>1715</v>
+      </c>
     </row>
     <row r="314" spans="1:51">
       <c r="A314">
@@ -49362,6 +49530,12 @@
       <c r="AW314">
         <v>1886</v>
       </c>
+      <c r="AX314">
+        <v>1762</v>
+      </c>
+      <c r="AY314">
+        <v>1715</v>
+      </c>
     </row>
     <row r="315" spans="1:51">
       <c r="A315">
@@ -51914,10 +52088,16 @@
         <v>1</v>
       </c>
       <c r="AV331">
+        <v>1931</v>
+      </c>
+      <c r="AW331">
         <v>1919</v>
       </c>
-      <c r="AW331">
+      <c r="AX331">
         <v>1888</v>
+      </c>
+      <c r="AY331">
+        <v>1712</v>
       </c>
     </row>
     <row r="332" spans="1:51">
@@ -52063,10 +52243,16 @@
         <v>1888</v>
       </c>
       <c r="AV332">
+        <v>1931</v>
+      </c>
+      <c r="AW332">
         <v>1919</v>
       </c>
-      <c r="AW332">
+      <c r="AX332">
         <v>1888</v>
+      </c>
+      <c r="AY332">
+        <v>1712</v>
       </c>
     </row>
     <row r="333" spans="1:51">
@@ -55085,9 +55271,15 @@
         <v>1</v>
       </c>
       <c r="AV352">
+        <v>1897</v>
+      </c>
+      <c r="AW352">
         <v>1856</v>
       </c>
-      <c r="AW352">
+      <c r="AX352">
+        <v>1836</v>
+      </c>
+      <c r="AY352">
         <v>1669</v>
       </c>
     </row>
@@ -55234,9 +55426,15 @@
         <v>1669</v>
       </c>
       <c r="AV353">
+        <v>1897</v>
+      </c>
+      <c r="AW353">
         <v>1856</v>
       </c>
-      <c r="AW353">
+      <c r="AX353">
+        <v>1836</v>
+      </c>
+      <c r="AY353">
         <v>1669</v>
       </c>
     </row>
@@ -55383,9 +55581,15 @@
         <v>1669</v>
       </c>
       <c r="AV354">
+        <v>1897</v>
+      </c>
+      <c r="AW354">
         <v>1856</v>
       </c>
-      <c r="AW354">
+      <c r="AX354">
+        <v>1836</v>
+      </c>
+      <c r="AY354">
         <v>1669</v>
       </c>
     </row>
@@ -55532,9 +55736,15 @@
         <v>1669</v>
       </c>
       <c r="AV355">
+        <v>1897</v>
+      </c>
+      <c r="AW355">
         <v>1856</v>
       </c>
-      <c r="AW355">
+      <c r="AX355">
+        <v>1836</v>
+      </c>
+      <c r="AY355">
         <v>1669</v>
       </c>
     </row>
@@ -59126,9 +59336,15 @@
         <v>1</v>
       </c>
       <c r="AV379">
+        <v>1986</v>
+      </c>
+      <c r="AW379">
         <v>1915</v>
       </c>
-      <c r="AW379">
+      <c r="AX379">
+        <v>1855</v>
+      </c>
+      <c r="AY379">
         <v>1741</v>
       </c>
     </row>
@@ -59275,9 +59491,15 @@
         <v>1741</v>
       </c>
       <c r="AV380">
+        <v>1986</v>
+      </c>
+      <c r="AW380">
         <v>1915</v>
       </c>
-      <c r="AW380">
+      <c r="AX380">
+        <v>1855</v>
+      </c>
+      <c r="AY380">
         <v>1741</v>
       </c>
     </row>
@@ -59424,9 +59646,15 @@
         <v>1741</v>
       </c>
       <c r="AV381">
+        <v>1986</v>
+      </c>
+      <c r="AW381">
         <v>1915</v>
       </c>
-      <c r="AW381">
+      <c r="AX381">
+        <v>1855</v>
+      </c>
+      <c r="AY381">
         <v>1741</v>
       </c>
     </row>
@@ -66773,9 +67001,15 @@
         <v>1</v>
       </c>
       <c r="AV430">
+        <v>2007</v>
+      </c>
+      <c r="AW430">
+        <v>1927</v>
+      </c>
+      <c r="AX430">
         <v>1776</v>
       </c>
-      <c r="AW430">
+      <c r="AY430">
         <v>1766</v>
       </c>
     </row>
@@ -66922,9 +67156,15 @@
         <v>1766</v>
       </c>
       <c r="AV431">
+        <v>2007</v>
+      </c>
+      <c r="AW431">
+        <v>1927</v>
+      </c>
+      <c r="AX431">
         <v>1776</v>
       </c>
-      <c r="AW431">
+      <c r="AY431">
         <v>1766</v>
       </c>
     </row>
@@ -67071,9 +67311,15 @@
         <v>1766</v>
       </c>
       <c r="AV432">
+        <v>2007</v>
+      </c>
+      <c r="AW432">
+        <v>1927</v>
+      </c>
+      <c r="AX432">
         <v>1776</v>
       </c>
-      <c r="AW432">
+      <c r="AY432">
         <v>1766</v>
       </c>
     </row>
@@ -67220,9 +67466,15 @@
         <v>1766</v>
       </c>
       <c r="AV433">
+        <v>2007</v>
+      </c>
+      <c r="AW433">
+        <v>1927</v>
+      </c>
+      <c r="AX433">
         <v>1776</v>
       </c>
-      <c r="AW433">
+      <c r="AY433">
         <v>1766</v>
       </c>
     </row>
@@ -80232,9 +80484,15 @@
         <v>0</v>
       </c>
       <c r="AV519">
+        <v>2035</v>
+      </c>
+      <c r="AW519">
+        <v>1989</v>
+      </c>
+      <c r="AX519">
         <v>1933</v>
       </c>
-      <c r="AW519">
+      <c r="AY519">
         <v>1907</v>
       </c>
     </row>
@@ -80381,9 +80639,15 @@
         <v>1907</v>
       </c>
       <c r="AV520">
+        <v>2035</v>
+      </c>
+      <c r="AW520">
+        <v>1989</v>
+      </c>
+      <c r="AX520">
         <v>1933</v>
       </c>
-      <c r="AW520">
+      <c r="AY520">
         <v>1907</v>
       </c>
     </row>
@@ -80530,9 +80794,15 @@
         <v>1907</v>
       </c>
       <c r="AV521">
+        <v>2035</v>
+      </c>
+      <c r="AW521">
+        <v>1989</v>
+      </c>
+      <c r="AX521">
         <v>1933</v>
       </c>
-      <c r="AW521">
+      <c r="AY521">
         <v>1907</v>
       </c>
     </row>
@@ -80679,9 +80949,15 @@
         <v>1907</v>
       </c>
       <c r="AV522">
+        <v>2035</v>
+      </c>
+      <c r="AW522">
+        <v>1989</v>
+      </c>
+      <c r="AX522">
         <v>1933</v>
       </c>
-      <c r="AW522">
+      <c r="AY522">
         <v>1907</v>
       </c>
     </row>
@@ -80828,9 +81104,15 @@
         <v>1907</v>
       </c>
       <c r="AV523">
+        <v>2035</v>
+      </c>
+      <c r="AW523">
+        <v>1989</v>
+      </c>
+      <c r="AX523">
         <v>1933</v>
       </c>
-      <c r="AW523">
+      <c r="AY523">
         <v>1907</v>
       </c>
     </row>
@@ -80977,9 +81259,15 @@
         <v>1907</v>
       </c>
       <c r="AV524">
+        <v>2035</v>
+      </c>
+      <c r="AW524">
+        <v>1989</v>
+      </c>
+      <c r="AX524">
         <v>1933</v>
       </c>
-      <c r="AW524">
+      <c r="AY524">
         <v>1907</v>
       </c>
     </row>
@@ -81126,9 +81414,15 @@
         <v>1907</v>
       </c>
       <c r="AV525">
+        <v>2035</v>
+      </c>
+      <c r="AW525">
+        <v>1989</v>
+      </c>
+      <c r="AX525">
         <v>1933</v>
       </c>
-      <c r="AW525">
+      <c r="AY525">
         <v>1907</v>
       </c>
     </row>
@@ -83533,6 +83827,12 @@
       <c r="AW541">
         <v>1944</v>
       </c>
+      <c r="AX541">
+        <v>1914</v>
+      </c>
+      <c r="AY541">
+        <v>1631</v>
+      </c>
     </row>
     <row r="542" spans="1:51">
       <c r="A542">
@@ -83682,6 +83982,12 @@
       <c r="AW542">
         <v>1944</v>
       </c>
+      <c r="AX542">
+        <v>1914</v>
+      </c>
+      <c r="AY542">
+        <v>1631</v>
+      </c>
     </row>
     <row r="543" spans="1:51">
       <c r="A543">
@@ -83831,6 +84137,12 @@
       <c r="AW543">
         <v>1944</v>
       </c>
+      <c r="AX543">
+        <v>1914</v>
+      </c>
+      <c r="AY543">
+        <v>1631</v>
+      </c>
     </row>
     <row r="544" spans="1:51">
       <c r="A544">
@@ -83980,6 +84292,12 @@
       <c r="AW544">
         <v>1944</v>
       </c>
+      <c r="AX544">
+        <v>1914</v>
+      </c>
+      <c r="AY544">
+        <v>1631</v>
+      </c>
     </row>
     <row r="545" spans="1:51">
       <c r="A545">
@@ -84129,6 +84447,12 @@
       <c r="AW545">
         <v>1944</v>
       </c>
+      <c r="AX545">
+        <v>1914</v>
+      </c>
+      <c r="AY545">
+        <v>1631</v>
+      </c>
     </row>
     <row r="546" spans="1:51">
       <c r="A546">
@@ -84278,6 +84602,12 @@
       <c r="AW546">
         <v>1944</v>
       </c>
+      <c r="AX546">
+        <v>1914</v>
+      </c>
+      <c r="AY546">
+        <v>1631</v>
+      </c>
     </row>
     <row r="547" spans="1:51">
       <c r="A547">
@@ -84427,6 +84757,12 @@
       <c r="AW547">
         <v>1944</v>
       </c>
+      <c r="AX547">
+        <v>1914</v>
+      </c>
+      <c r="AY547">
+        <v>1631</v>
+      </c>
     </row>
     <row r="548" spans="1:51">
       <c r="A548">
@@ -84576,6 +84912,12 @@
       <c r="AW548">
         <v>1944</v>
       </c>
+      <c r="AX548">
+        <v>1914</v>
+      </c>
+      <c r="AY548">
+        <v>1631</v>
+      </c>
     </row>
     <row r="549" spans="1:51">
       <c r="A549">
@@ -96629,9 +96971,15 @@
         <v>0</v>
       </c>
       <c r="AV628">
+        <v>1975</v>
+      </c>
+      <c r="AW628">
+        <v>1771</v>
+      </c>
+      <c r="AX628">
         <v>1759</v>
       </c>
-      <c r="AW628">
+      <c r="AY628">
         <v>1616</v>
       </c>
     </row>
@@ -96778,9 +97126,15 @@
         <v>1616</v>
       </c>
       <c r="AV629">
+        <v>1975</v>
+      </c>
+      <c r="AW629">
+        <v>1771</v>
+      </c>
+      <c r="AX629">
         <v>1759</v>
       </c>
-      <c r="AW629">
+      <c r="AY629">
         <v>1616</v>
       </c>
     </row>
@@ -96903,9 +97257,15 @@
         <v>0</v>
       </c>
       <c r="AV630">
+        <v>1972</v>
+      </c>
+      <c r="AW630">
+        <v>1766</v>
+      </c>
+      <c r="AX630">
         <v>1760</v>
       </c>
-      <c r="AW630">
+      <c r="AY630">
         <v>1655</v>
       </c>
     </row>
@@ -97052,9 +97412,15 @@
         <v>1655</v>
       </c>
       <c r="AV631">
+        <v>1972</v>
+      </c>
+      <c r="AW631">
+        <v>1766</v>
+      </c>
+      <c r="AX631">
         <v>1760</v>
       </c>
-      <c r="AW631">
+      <c r="AY631">
         <v>1655</v>
       </c>
     </row>
@@ -97201,9 +97567,15 @@
         <v>1655</v>
       </c>
       <c r="AV632">
+        <v>1972</v>
+      </c>
+      <c r="AW632">
+        <v>1766</v>
+      </c>
+      <c r="AX632">
         <v>1760</v>
       </c>
-      <c r="AW632">
+      <c r="AY632">
         <v>1655</v>
       </c>
     </row>
@@ -97350,9 +97722,15 @@
         <v>1655</v>
       </c>
       <c r="AV633">
+        <v>1972</v>
+      </c>
+      <c r="AW633">
+        <v>1766</v>
+      </c>
+      <c r="AX633">
         <v>1760</v>
       </c>
-      <c r="AW633">
+      <c r="AY633">
         <v>1655</v>
       </c>
     </row>
@@ -110027,6 +110405,18 @@
       <c r="AS717">
         <v>0</v>
       </c>
+      <c r="AV717">
+        <v>1981</v>
+      </c>
+      <c r="AW717">
+        <v>1834</v>
+      </c>
+      <c r="AX717">
+        <v>1801</v>
+      </c>
+      <c r="AY717">
+        <v>1733</v>
+      </c>
     </row>
     <row r="718" spans="1:51">
       <c r="A718">
@@ -110147,9 +110537,15 @@
         <v>0</v>
       </c>
       <c r="AV718">
+        <v>1988</v>
+      </c>
+      <c r="AW718">
+        <v>1853</v>
+      </c>
+      <c r="AX718">
         <v>1671</v>
       </c>
-      <c r="AW718">
+      <c r="AY718">
         <v>1647</v>
       </c>
     </row>
@@ -110296,9 +110692,15 @@
         <v>1647</v>
       </c>
       <c r="AV719">
+        <v>1988</v>
+      </c>
+      <c r="AW719">
+        <v>1853</v>
+      </c>
+      <c r="AX719">
         <v>1671</v>
       </c>
-      <c r="AW719">
+      <c r="AY719">
         <v>1647</v>
       </c>
     </row>
@@ -110445,9 +110847,15 @@
         <v>1647</v>
       </c>
       <c r="AV720">
+        <v>1988</v>
+      </c>
+      <c r="AW720">
+        <v>1853</v>
+      </c>
+      <c r="AX720">
         <v>1671</v>
       </c>
-      <c r="AW720">
+      <c r="AY720">
         <v>1647</v>
       </c>
     </row>
